--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6790,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>206 SABER Y FANTASIA CON MARIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.10163</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.01118</v>
-      </c>
-      <c r="I2" t="n">
-        <v>201</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.10163</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.01118</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>207 ALFREDO PINILLOS GOICOCHEA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.10787</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.01937</v>
-      </c>
-      <c r="I3" t="n">
-        <v>238</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.10787</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.01937</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>209 SANTA ANA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.1168</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.0271</v>
-      </c>
-      <c r="I4" t="n">
-        <v>415</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.1168</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.0271</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>215</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.09693</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.02016</v>
-      </c>
-      <c r="I5" t="n">
-        <v>287</v>
-      </c>
-      <c r="J5" t="n">
-        <v>13</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.09693</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.02016</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>252 NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.107839999999999</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.01593</v>
-      </c>
-      <c r="I6" t="n">
-        <v>340</v>
-      </c>
-      <c r="J6" t="n">
-        <v>14</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.10784</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.01593</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>253 ISABEL HONORIO DE LAZARTE</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.103120000000002</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.00797</v>
-      </c>
-      <c r="I7" t="n">
-        <v>371</v>
-      </c>
-      <c r="J7" t="n">
-        <v>18</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.103120000000002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.00797</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>1564 RADIANTES CAPULLITOS</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.09104</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.0093</v>
-      </c>
-      <c r="I8" t="n">
-        <v>423</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.09104</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.0093</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>1733 MI MUNDO MARAVILLOSO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.124510000000003</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.03323</v>
-      </c>
-      <c r="I9" t="n">
-        <v>226</v>
-      </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.124510000000003</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.03323</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>GUSTAVO RIES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.101889999999999</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.00614</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1890</v>
-      </c>
-      <c r="J10" t="n">
-        <v>87</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.10189</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.00614</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.122920000000002</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.02488</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2080</v>
-      </c>
-      <c r="J11" t="n">
-        <v>95</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.122920000000002</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.02488</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2080</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>LICEO TRUJILLO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.09756</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.03292999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2462</v>
-      </c>
-      <c r="J12" t="n">
-        <v>117</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.09756</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.03293</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2462</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>80002 ANTONIO TORRES ARAUJO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.1211</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.02563000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1364</v>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.1211</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.02563</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>80003 ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.11725</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.02449</v>
-      </c>
-      <c r="I14" t="n">
-        <v>337</v>
-      </c>
-      <c r="J14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.11725</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.02449</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>80005 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.114240000000002</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.01542000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>312</v>
-      </c>
-      <c r="J15" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.114240000000002</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.01542</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>80008 REPUBLICA DE ARGENTINA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.10496</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.00824</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2032</v>
-      </c>
-      <c r="J16" t="n">
-        <v>74</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.10496</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.00824</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>80010 RICARDO PALMA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.101039999999999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.02131</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J17" t="n">
-        <v>56</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.10104</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.02131</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>80014 JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.108176</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.04526</v>
-      </c>
-      <c r="I18" t="n">
-        <v>496</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.108176</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.04526</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>80017 ALFREDO TELLO SALAVARRIA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.105399999999999</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.04109</v>
-      </c>
-      <c r="I19" t="n">
-        <v>784</v>
-      </c>
-      <c r="J19" t="n">
-        <v>37</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.1054</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.04109</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>80018 REPUBLICA DE MEXICO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.103999999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.04130000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>560</v>
-      </c>
-      <c r="J20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.104</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.0413</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>80019 CIRO ALEGRIA BAZAN</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.11425</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.00526000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>436</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.11425</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.00526</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>80077 ALCIDES CARREÑO BLAS</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.11234</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.02209000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>333</v>
-      </c>
-      <c r="J22" t="n">
-        <v>16</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.11234</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.02209</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>80626 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.09003</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.01133</v>
-      </c>
-      <c r="I23" t="n">
-        <v>638</v>
-      </c>
-      <c r="J23" t="n">
-        <v>29</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.09003</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.01133</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>80865 DANIEL HOYLE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.09549</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.015024</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1436</v>
-      </c>
-      <c r="J24" t="n">
-        <v>64</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.09549</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.015024</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>80882 JORGE CHAVEZ</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.09287</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.99507</v>
-      </c>
-      <c r="I25" t="n">
-        <v>668</v>
-      </c>
-      <c r="J25" t="n">
-        <v>36</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.09287</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.99507</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>80892 LOS PINOS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.12433</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.04182</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1103</v>
-      </c>
-      <c r="J26" t="n">
-        <v>50</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.12433</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.04182</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>81001 REPUBLICA DE PANAMA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.117100000000002</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.0269</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1434</v>
-      </c>
-      <c r="J27" t="n">
-        <v>62</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.117100000000002</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.0269</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>81002 JAVIER HERAUD</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.1181</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.01949999999999</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1452</v>
-      </c>
-      <c r="J28" t="n">
-        <v>70</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.1181</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.0195</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>81003 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.10813883264305</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-79.015925025085</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1437</v>
-      </c>
-      <c r="J29" t="n">
-        <v>57</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.10813883264305</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.015925025085</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1437</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>81004 LA UNION</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.107021</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.020124</v>
-      </c>
-      <c r="I30" t="n">
-        <v>353</v>
-      </c>
-      <c r="J30" t="n">
-        <v>15</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.107021</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.020124</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>81005 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.104134</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-79.01444499999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>421</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.104134</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-79.014445</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>81006 AMAUTA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.1031</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-79.01300000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>282</v>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.1031</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-79.013</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>81007 MODELO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.104905</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.0243</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1921</v>
-      </c>
-      <c r="J33" t="n">
-        <v>104</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.104905</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.0243</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>81008 / 81008 MUNICIPAL</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-8.10647</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-79.02200000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>625</v>
-      </c>
-      <c r="J34" t="n">
-        <v>30</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-8.10647</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-79.022</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>81010 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-8.11834</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-79.04434000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>404</v>
-      </c>
-      <c r="J35" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-8.11834</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-79.04434</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>81011 ANTONIO RAYMONDI</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-8.107379999999999</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-79.02934999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>962</v>
-      </c>
-      <c r="J36" t="n">
-        <v>42</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-8.10738</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-79.02935</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>81015 CARLOS E. UCEDA MEZA</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-8.124359999999999</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-79.0284</v>
-      </c>
-      <c r="I37" t="n">
-        <v>802</v>
-      </c>
-      <c r="J37" t="n">
-        <v>41</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.12436</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-79.0284</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-8.123239999999999</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-79.03234999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>339</v>
-      </c>
-      <c r="J38" t="n">
-        <v>14</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-8.12324</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-79.03235</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>81746 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-8.111660000000002</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-79.04173</v>
-      </c>
-      <c r="I39" t="n">
-        <v>290</v>
-      </c>
-      <c r="J39" t="n">
-        <v>17</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-8.111660000000002</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-79.04173</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>81755 MEDALLA MILAGROSA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-8.092829999999999</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-79.0046</v>
-      </c>
-      <c r="I40" t="n">
-        <v>558</v>
-      </c>
-      <c r="J40" t="n">
-        <v>30</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-8.09283</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-79.0046</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>MARCIAL ACHARAN Y SMITH</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-8.107849999999999</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-79.02515</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2034</v>
-      </c>
-      <c r="J41" t="n">
-        <v>119</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-8.10785</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-79.02515</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SAN NICOLAS</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-8.109310000000002</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-79.03556</v>
-      </c>
-      <c r="I42" t="n">
-        <v>330</v>
-      </c>
-      <c r="J42" t="n">
-        <v>16</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-8.109310000000002</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-79.03556</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-8.11295</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-79.02612000000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1898</v>
-      </c>
-      <c r="J43" t="n">
-        <v>96</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-8.11295</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-79.02612</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-8.106057</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-79.023275</v>
-      </c>
-      <c r="I44" t="n">
-        <v>553</v>
-      </c>
-      <c r="J44" t="n">
-        <v>37</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-8.106057</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-79.023275</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>CECAT MARCIAL ACHARAN</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-8.12433</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-79.02455999999999</v>
-      </c>
-      <c r="I45" t="n">
-        <v>623</v>
-      </c>
-      <c r="J45" t="n">
-        <v>38</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-8.12433</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-79.02456</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>210 DULCE VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-8.11656</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-79.02179</v>
-      </c>
-      <c r="I46" t="n">
-        <v>221</v>
-      </c>
-      <c r="J46" t="n">
-        <v>11</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-8.11656</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-79.02179</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-8.09545</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-79.04459</v>
-      </c>
-      <c r="I47" t="n">
-        <v>761</v>
-      </c>
-      <c r="J47" t="n">
-        <v>37</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-8.09545</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-79.04459</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>82050 HUERTA BELLA</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-8.088279999999999</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-79.00109999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>237</v>
-      </c>
-      <c r="J48" t="n">
-        <v>10</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-8.08828</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-79.0011</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>MARIA NEGRON UGARTE</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-8.107089999999999</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-79.00709000000001</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1454</v>
-      </c>
-      <c r="J49" t="n">
-        <v>83</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-8.10709</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-79.00709</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>81584 EVERARDO ZAPATA SANTILLANA</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-8.09984</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-79.04849</v>
-      </c>
-      <c r="I50" t="n">
-        <v>421</v>
-      </c>
-      <c r="J50" t="n">
-        <v>19</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-8.09984</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-79.04849</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>DANTE ALIGHIERI</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-8.122719999999999</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-79.02269</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1191</v>
-      </c>
-      <c r="J51" t="n">
-        <v>54</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-8.12272</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-79.02269</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-8.118650000000002</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-79.03451</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J52" t="n">
-        <v>71</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-8.118650000000002</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-79.03451</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>SANTA MARIA DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-8.121840000000002</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-79.01985000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>274</v>
-      </c>
-      <c r="J53" t="n">
-        <v>14</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-8.121840000000002</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-79.01985</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>LA ASUNCION</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-8.104509999999999</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-79.03596</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1049</v>
-      </c>
-      <c r="J54" t="n">
-        <v>70</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-8.10451</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-79.03596</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-8.10909</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-79.03924000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>303</v>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-8.10909</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-79.03924</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>SANTA ROSA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-8.113479999999999</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-79.02592</v>
-      </c>
-      <c r="I56" t="n">
-        <v>280</v>
-      </c>
-      <c r="J56" t="n">
-        <v>25</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-8.11348</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-79.02592</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>ADVENTISTA JOSE DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-8.106695999999999</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-79.02538199999999</v>
-      </c>
-      <c r="I57" t="n">
-        <v>500</v>
-      </c>
-      <c r="J57" t="n">
-        <v>27</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-8.106696</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-79.025382</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>ALEJANDRO DEUSTUA</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-8.11717</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-79.02265</v>
-      </c>
-      <c r="I58" t="n">
-        <v>222</v>
-      </c>
-      <c r="J58" t="n">
-        <v>16</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-8.11717</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-79.02265</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>KINDERLAND</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-8.12466</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-79.02916</v>
-      </c>
-      <c r="I59" t="n">
-        <v>29</v>
-      </c>
-      <c r="J59" t="n">
-        <v>3</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-8.12466</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-79.02916</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-8.092980000000003</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-79.01129</v>
-      </c>
-      <c r="I60" t="n">
-        <v>244</v>
-      </c>
-      <c r="J60" t="n">
-        <v>27</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-8.092980000000003</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-79.01129</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>EIFFEL SCHOOLS</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-8.109870000000003</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-79.00984</v>
-      </c>
-      <c r="I61" t="n">
-        <v>601</v>
-      </c>
-      <c r="J61" t="n">
-        <v>35</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-8.109870000000003</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-79.00984</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>INGENIERIA</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-8.121560000000002</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-79.03677999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>656</v>
-      </c>
-      <c r="J62" t="n">
-        <v>38</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-8.121560000000002</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-79.03678</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>LAS CAPULLANAS</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-8.109920000000002</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-79.04155</v>
-      </c>
-      <c r="I63" t="n">
-        <v>252</v>
-      </c>
-      <c r="J63" t="n">
-        <v>20</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-8.109920000000002</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-79.04155</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-8.10272</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-79.03377999999999</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1296</v>
-      </c>
-      <c r="J64" t="n">
-        <v>88</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-8.10272</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-79.03378</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-8.11811</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-79.04255999999999</v>
-      </c>
-      <c r="I65" t="n">
-        <v>387</v>
-      </c>
-      <c r="J65" t="n">
-        <v>27</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-8.11811</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-79.04256</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>MIS ABEJITAS</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-8.09656</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-79.04158</v>
-      </c>
-      <c r="I66" t="n">
-        <v>272</v>
-      </c>
-      <c r="J66" t="n">
-        <v>16</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-8.09656</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-79.04158</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>MARIA MADRE</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-8.08887</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-79.02103</v>
-      </c>
-      <c r="I67" t="n">
-        <v>752</v>
-      </c>
-      <c r="J67" t="n">
-        <v>35</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-8.08887</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-79.02103</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>PORTAL DE BELEN</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-8.095219999999999</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-79.01618000000001</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1033</v>
-      </c>
-      <c r="J68" t="n">
-        <v>64</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-8.09522</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-79.01618</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-8.11012</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-79.01557</v>
-      </c>
-      <c r="I69" t="n">
-        <v>214</v>
-      </c>
-      <c r="J69" t="n">
-        <v>16</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-8.11012</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-79.01557</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-8.12655</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-79.03494000000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>641</v>
-      </c>
-      <c r="J70" t="n">
-        <v>74</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-8.12655</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-79.03494</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>TALENTOS</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-8.13195</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-79.02874</v>
-      </c>
-      <c r="I71" t="n">
-        <v>812</v>
-      </c>
-      <c r="J71" t="n">
-        <v>55</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-8.13195</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-79.02874</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>WILLIAM HARVEY</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-8.122159999999999</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-79.04248</v>
-      </c>
-      <c r="I72" t="n">
-        <v>419</v>
-      </c>
-      <c r="J72" t="n">
-        <v>35</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-8.12216</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-79.04248</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>SAN GERARDO</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-8.10093</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-79.03815</v>
-      </c>
-      <c r="I73" t="n">
-        <v>204</v>
-      </c>
-      <c r="J73" t="n">
-        <v>16</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-8.10093</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-79.03815</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>SANTA CLARA</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-8.10797</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-79.02731</v>
-      </c>
-      <c r="I74" t="n">
-        <v>90</v>
-      </c>
-      <c r="J74" t="n">
-        <v>10</v>
-      </c>
-      <c r="K74" t="n">
-        <v>1</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-8.10797</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-79.02731</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>HERMANOS BLANCO</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-8.097519999999999</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-79.03628999999999</v>
-      </c>
-      <c r="I75" t="n">
-        <v>833</v>
-      </c>
-      <c r="J75" t="n">
-        <v>53</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-8.09752</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-79.03629</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>UNIVERSAL SCHOOL</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-8.122</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-79.02307</v>
-      </c>
-      <c r="I76" t="n">
-        <v>310</v>
-      </c>
-      <c r="J76" t="n">
-        <v>7</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-8.122</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-79.02307</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-8.103440000000003</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-79.03421</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1464</v>
-      </c>
-      <c r="J77" t="n">
-        <v>69</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-8.103440000000003</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-79.03421</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1464</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>SAN CARLOS Y SAN MARCELO</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-8.10816</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-79.02894000000001</v>
-      </c>
-      <c r="I78" t="n">
-        <v>389</v>
-      </c>
-      <c r="J78" t="n">
-        <v>40</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-8.10816</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-79.02894</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SAN LUIS</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-8.097329999999999</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-79.0183</v>
-      </c>
-      <c r="I79" t="n">
-        <v>388</v>
-      </c>
-      <c r="J79" t="n">
-        <v>23</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-8.09733</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-79.0183</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-8.0954</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-79.01109</v>
-      </c>
-      <c r="I80" t="n">
-        <v>748</v>
-      </c>
-      <c r="J80" t="n">
-        <v>37</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-8.0954</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-79.01109</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>RAFAEL NARVAEZ CADENILLAS</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-8.11777</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-79.04216</v>
-      </c>
-      <c r="I81" t="n">
-        <v>1234</v>
-      </c>
-      <c r="J81" t="n">
-        <v>90</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-8.11777</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-79.04216</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>LOS LIBERTADORES</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-8.124090000000002</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-79.02226</v>
-      </c>
-      <c r="I82" t="n">
-        <v>7</v>
-      </c>
-      <c r="J82" t="n">
-        <v>8</v>
-      </c>
-      <c r="K82" t="n">
-        <v>2</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-8.124090000000002</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-79.02226</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>MAYOR DE SAN MARCOS</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-8.116569999999999</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-79.02464000000001</v>
-      </c>
-      <c r="I83" t="n">
-        <v>503</v>
-      </c>
-      <c r="J83" t="n">
-        <v>35</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-8.11657</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-79.02464</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>SAN FELIPE</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-8.11863</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-79.02392999999999</v>
-      </c>
-      <c r="I84" t="n">
-        <v>351</v>
-      </c>
-      <c r="J84" t="n">
-        <v>22</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-8.11863</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-79.02393</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>80824 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-8.08649</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-79.00268</v>
-      </c>
-      <c r="I85" t="n">
-        <v>2504</v>
-      </c>
-      <c r="J85" t="n">
-        <v>94</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-8.08649</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-79.00268</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2504</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>SAN ESTEBAN</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-8.088329999999999</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-79.01571</v>
-      </c>
-      <c r="I86" t="n">
-        <v>355</v>
-      </c>
-      <c r="J86" t="n">
-        <v>16</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-8.08833</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-79.01571</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>80033 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-8.081</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-79.11715</v>
-      </c>
-      <c r="I87" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J87" t="n">
-        <v>44</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-8.081</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-79.11715</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>80628</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-8.080947</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-79.08485400000001</v>
-      </c>
-      <c r="I88" t="n">
-        <v>349</v>
-      </c>
-      <c r="J88" t="n">
-        <v>14</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-8.080947</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-79.084854</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>80848 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-8.09174</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-79.07549</v>
-      </c>
-      <c r="I89" t="n">
-        <v>227</v>
-      </c>
-      <c r="J89" t="n">
-        <v>10</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-8.09174</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-79.07549</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>80869 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-8.125003</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-78.949009</v>
-      </c>
-      <c r="I90" t="n">
-        <v>359</v>
-      </c>
-      <c r="J90" t="n">
-        <v>20</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-8.125003</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-78.949009</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>81605 SAN ILDEFONSO</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-8.080159</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-78.951185</v>
-      </c>
-      <c r="I91" t="n">
-        <v>271</v>
-      </c>
-      <c r="J91" t="n">
-        <v>15</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-8.080159</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-78.951185</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>81523 JOSE IGNACIO CHOPITEA</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-8.088100000000003</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-78.9691</v>
-      </c>
-      <c r="I92" t="n">
-        <v>428</v>
-      </c>
-      <c r="J92" t="n">
-        <v>23</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-8.088100000000003</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-78.9691</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>81526 VICTOR GANOZA PLAZA</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-8.103</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-78.9121</v>
-      </c>
-      <c r="I93" t="n">
-        <v>292</v>
-      </c>
-      <c r="J93" t="n">
-        <v>16</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-8.103</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-78.9121</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>1721 LINA SKRABONJA</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-8.16952</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-79.01058999999999</v>
-      </c>
-      <c r="I94" t="n">
-        <v>222</v>
-      </c>
-      <c r="J94" t="n">
-        <v>9</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-8.16952</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-79.01059</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>80048 JOSE EULOGIO GARRIDO</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-8.147622</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-79.00412799999999</v>
-      </c>
-      <c r="I95" t="n">
-        <v>675</v>
-      </c>
-      <c r="J95" t="n">
-        <v>29</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-8.147622</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-79.004128</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>JOSE EMILIO LEFEBVRE FRANCOEUR</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-8.172499999999999</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-79.00904</v>
-      </c>
-      <c r="I96" t="n">
-        <v>1179</v>
-      </c>
-      <c r="J96" t="n">
-        <v>41</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-8.1725</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-79.00904</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>1638 PASITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-8.12387</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-79.0415</v>
-      </c>
-      <c r="I97" t="n">
-        <v>229</v>
-      </c>
-      <c r="J97" t="n">
-        <v>12</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-8.12387</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-79.0415</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-8.131</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-79.04407999999999</v>
-      </c>
-      <c r="I98" t="n">
-        <v>425</v>
-      </c>
-      <c r="J98" t="n">
-        <v>20</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-8.131</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-79.04408</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>CLARETIANO</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-8.12918</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-79.03632</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1235</v>
-      </c>
-      <c r="J99" t="n">
-        <v>82</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-8.12918</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-79.03632</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>80006 NUEVO PERU</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-8.106030000000002</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-79.01125</v>
-      </c>
-      <c r="I100" t="n">
-        <v>763</v>
-      </c>
-      <c r="J100" t="n">
-        <v>30</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-8.106030000000002</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-79.01125</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>ENGELS CLASS</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-8.086824</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-79.00284000000001</v>
-      </c>
-      <c r="I101" t="n">
-        <v>260</v>
-      </c>
-      <c r="J101" t="n">
-        <v>10</v>
-      </c>
-      <c r="K101" t="n">
-        <v>1</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-8.086824</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-79.00284</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>PERUANO AMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-8.1068</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-79.03232</v>
-      </c>
-      <c r="I102" t="n">
-        <v>562</v>
-      </c>
-      <c r="J102" t="n">
-        <v>24</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-8.1068</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-79.03232</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>HANS HEINRICH BRUNING</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-8.12683</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-79.02997999999999</v>
-      </c>
-      <c r="I103" t="n">
-        <v>564</v>
-      </c>
-      <c r="J103" t="n">
-        <v>33</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-8.12683</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-79.02998</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>KEPLER</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-8.11345</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-79.03152</v>
-      </c>
-      <c r="I104" t="n">
-        <v>274</v>
-      </c>
-      <c r="J104" t="n">
-        <v>20</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-8.11345</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-79.03152</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>SANTA TERESITA</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-8.087289999999999</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-79.01658999999999</v>
-      </c>
-      <c r="I105" t="n">
-        <v>333</v>
-      </c>
-      <c r="J105" t="n">
-        <v>24</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-8.08729</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-79.01659</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>SAN JUAN</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-8.103999999999999</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-79.02893899999999</v>
-      </c>
-      <c r="I106" t="n">
-        <v>2187</v>
-      </c>
-      <c r="J106" t="n">
-        <v>128</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-8.104</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-79.028939</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-8.102392999999999</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-79.005064</v>
-      </c>
-      <c r="I107" t="n">
-        <v>410</v>
-      </c>
-      <c r="J107" t="n">
-        <v>27</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-8.102393</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-79.005064</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>INTEGRAL CLASS</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-8.11736</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-79.03386</v>
-      </c>
-      <c r="I108" t="n">
-        <v>447</v>
-      </c>
-      <c r="J108" t="n">
-        <v>27</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-8.11736</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-79.03386</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>447</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>SEBASTIAN SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-8.11645</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-79.02109</v>
-      </c>
-      <c r="I109" t="n">
-        <v>262</v>
-      </c>
-      <c r="J109" t="n">
-        <v>15</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-8.11645</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-79.02109</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>FRAY MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-8.091659999999999</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-79.00578</v>
-      </c>
-      <c r="I110" t="n">
-        <v>308</v>
-      </c>
-      <c r="J110" t="n">
-        <v>21</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-8.09166</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-79.00578</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>NUESTRA SEÑORA DE SCHOENSTATT</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-8.12233</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-79.03555</v>
-      </c>
-      <c r="I111" t="n">
-        <v>343</v>
-      </c>
-      <c r="J111" t="n">
-        <v>21</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-8.12233</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-79.03555</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>QUIPUS</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-8.088039999999999</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-79.00192</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" t="n">
-        <v>1</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-8.08804</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-79.00192</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>DESPERTAR</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-8.099410000000002</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-79.03782</v>
-      </c>
-      <c r="I113" t="n">
-        <v>65</v>
-      </c>
-      <c r="J113" t="n">
-        <v>8</v>
-      </c>
-      <c r="K113" t="n">
-        <v>1</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-8.099410000000002</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-79.03782</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-8.09474</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-79.00501</v>
-      </c>
-      <c r="I114" t="n">
-        <v>378</v>
-      </c>
-      <c r="J114" t="n">
-        <v>27</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-8.09474</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-79.00501</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>SAN CARLOS</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-8.172549999999999</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-79.0064</v>
-      </c>
-      <c r="I115" t="n">
-        <v>231</v>
-      </c>
-      <c r="J115" t="n">
-        <v>13</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-8.17255</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-79.0064</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>TRILCE</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-8.101760000000002</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-79.03523</v>
-      </c>
-      <c r="I116" t="n">
-        <v>346</v>
-      </c>
-      <c r="J116" t="n">
-        <v>27</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-8.101760000000002</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-79.03523</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>BILINGUE LOS ANDES</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-8.117620000000002</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-79.03292999999999</v>
-      </c>
-      <c r="I117" t="n">
-        <v>107</v>
-      </c>
-      <c r="J117" t="n">
-        <v>14</v>
-      </c>
-      <c r="K117" t="n">
-        <v>1</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-8.117620000000002</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-79.03293</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>JAN KOMENSKY</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-8.107570000000003</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-79.00779</v>
-      </c>
-      <c r="I118" t="n">
-        <v>321</v>
-      </c>
-      <c r="J118" t="n">
-        <v>20</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-8.107570000000003</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-79.00779</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>SIGNOS DE FE LA SALLE</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-8.091889999999999</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-79.04648</v>
-      </c>
-      <c r="I119" t="n">
-        <v>329</v>
-      </c>
-      <c r="J119" t="n">
-        <v>20</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-8.09189</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-79.04648</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>MONTEVERDE</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-8.09207</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-79.04213</v>
-      </c>
-      <c r="I120" t="n">
-        <v>303</v>
-      </c>
-      <c r="J120" t="n">
-        <v>29</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-8.09207</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-79.04213</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-8.12903</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-79.02064</v>
-      </c>
-      <c r="I121" t="n">
-        <v>204</v>
-      </c>
-      <c r="J121" t="n">
-        <v>21</v>
-      </c>
-      <c r="K121" t="n">
-        <v>1</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-8.12903</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-79.02064</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>TYCHO BRAHE</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-8.09599</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-79.02454</v>
-      </c>
-      <c r="I122" t="n">
-        <v>271</v>
-      </c>
-      <c r="J122" t="n">
-        <v>19</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-8.09599</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-79.02454</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>EL CULTURAL AMERICAN SCHOOL</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-8.11726</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-79.03255</v>
-      </c>
-      <c r="I123" t="n">
-        <v>539</v>
-      </c>
-      <c r="J123" t="n">
-        <v>40</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-8.11726</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-79.03255</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6865,20 +8073,30 @@
           <t>LOUIS PASTEUR</t>
         </is>
       </c>
-      <c r="G124" t="n">
-        <v>-8.09229</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-78.95740000000001</v>
-      </c>
-      <c r="I124" t="n">
-        <v>547</v>
-      </c>
-      <c r="J124" t="n">
-        <v>23</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-8.09229</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-78.9574</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6917,20 +8135,30 @@
           <t>81014 PEDRO MERCEDES UREÑA</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>-8.11221643601271</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-79.04872753899031</v>
-      </c>
-      <c r="I125" t="n">
-        <v>2363</v>
-      </c>
-      <c r="J125" t="n">
-        <v>92</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-8.11221643601271</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-79.0487275389903</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6969,20 +8197,30 @@
           <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G126" t="n">
-        <v>-8.12073</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-79.01998</v>
-      </c>
-      <c r="I126" t="n">
-        <v>245</v>
-      </c>
-      <c r="J126" t="n">
-        <v>26</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-8.12073</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-79.01998</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -7021,20 +8259,30 @@
           <t>INNOVA SCHOOLS - TRUJILLO</t>
         </is>
       </c>
-      <c r="G127" t="n">
-        <v>-8.134278</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-79.025868</v>
-      </c>
-      <c r="I127" t="n">
-        <v>977</v>
-      </c>
-      <c r="J127" t="n">
-        <v>29</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-8.134278</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-79.025868</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -7073,20 +8321,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>-8.172302999999999</v>
-      </c>
-      <c r="H128" t="n">
-        <v>-79.00876599999999</v>
-      </c>
-      <c r="I128" t="n">
-        <v>299</v>
-      </c>
-      <c r="J128" t="n">
-        <v>14</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-8.172303</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-79.008766</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -7125,20 +8383,30 @@
           <t>FUTURA SCHOOLS - SEDE SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>-8.095219999999999</v>
-      </c>
-      <c r="H129" t="n">
-        <v>-79.05383</v>
-      </c>
-      <c r="I129" t="n">
-        <v>495</v>
-      </c>
-      <c r="J129" t="n">
-        <v>26</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-8.09522</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>-79.05383</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -7177,20 +8445,30 @@
           <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
-      <c r="G130" t="n">
-        <v>-8.10614</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-79.024557</v>
-      </c>
-      <c r="I130" t="n">
-        <v>580</v>
-      </c>
-      <c r="J130" t="n">
-        <v>35</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-8.10614</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-79.024557</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -7229,20 +8507,30 @@
           <t>AI APAEC TRUJILLO CENTRO</t>
         </is>
       </c>
-      <c r="G131" t="n">
-        <v>-8.112819999999999</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-79.03315000000001</v>
-      </c>
-      <c r="I131" t="n">
-        <v>331</v>
-      </c>
-      <c r="J131" t="n">
-        <v>17</v>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-8.11282</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>-79.03315</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -7281,20 +8569,30 @@
           <t>ORION BEN CARSON</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>-8.09925</v>
-      </c>
-      <c r="H132" t="n">
-        <v>-79.02809999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>283</v>
-      </c>
-      <c r="J132" t="n">
-        <v>19</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-8.09925</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-79.0281</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -7333,20 +8631,30 @@
           <t>KINDERHOUSE</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>-8.171478</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-79.008951</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-8.171478</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-79.008951</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -7385,20 +8693,30 @@
           <t>NOBEL SCHOOL</t>
         </is>
       </c>
-      <c r="G134" t="n">
-        <v>-8.11101</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-79.03515</v>
-      </c>
-      <c r="I134" t="n">
-        <v>364</v>
-      </c>
-      <c r="J134" t="n">
-        <v>22</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-8.11101</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-79.03515</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -7437,20 +8755,30 @@
           <t>INNOVA SCHOOLS - TRUJILLO SANTA</t>
         </is>
       </c>
-      <c r="G135" t="n">
-        <v>-8.0951</v>
-      </c>
-      <c r="H135" t="n">
-        <v>-79.01537</v>
-      </c>
-      <c r="I135" t="n">
-        <v>1111</v>
-      </c>
-      <c r="J135" t="n">
-        <v>63</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-8.0951</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-79.01537</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -7489,20 +8817,30 @@
           <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
-      <c r="G136" t="n">
-        <v>-8.100059999999999</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-79.03645</v>
-      </c>
-      <c r="I136" t="n">
-        <v>668</v>
-      </c>
-      <c r="J136" t="n">
-        <v>26</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-8.10006</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-79.03645</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7541,20 +8879,30 @@
           <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
-      <c r="G137" t="n">
-        <v>-8.09717</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-79.03601999999999</v>
-      </c>
-      <c r="I137" t="n">
-        <v>626</v>
-      </c>
-      <c r="J137" t="n">
-        <v>29</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-8.09717</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-79.03602</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7593,20 +8941,30 @@
           <t>GRACIELA DIAZ</t>
         </is>
       </c>
-      <c r="G138" t="n">
-        <v>-8.102480999999999</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-79.005257</v>
-      </c>
-      <c r="I138" t="n">
-        <v>291</v>
-      </c>
-      <c r="J138" t="n">
-        <v>21</v>
-      </c>
-      <c r="K138" t="n">
-        <v>0</v>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-8.102481</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-79.005257</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7645,20 +9003,30 @@
           <t>JAN KOMENSKY</t>
         </is>
       </c>
-      <c r="G139" t="n">
-        <v>-8.109514000000003</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-79.002189</v>
-      </c>
-      <c r="I139" t="n">
-        <v>318</v>
-      </c>
-      <c r="J139" t="n">
-        <v>14</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-8.109514000000003</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-79.002189</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7697,20 +9065,30 @@
           <t>SAN PEDRO</t>
         </is>
       </c>
-      <c r="G140" t="n">
-        <v>-8.096869999999999</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-79.02194</v>
-      </c>
-      <c r="I140" t="n">
-        <v>353</v>
-      </c>
-      <c r="J140" t="n">
-        <v>27</v>
-      </c>
-      <c r="K140" t="n">
-        <v>0</v>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-8.09687</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-79.02194</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7749,20 +9127,30 @@
           <t>TRILCE</t>
         </is>
       </c>
-      <c r="G141" t="n">
-        <v>-8.102370000000002</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-79.03449000000001</v>
-      </c>
-      <c r="I141" t="n">
-        <v>282</v>
-      </c>
-      <c r="J141" t="n">
-        <v>22</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0</v>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-8.102370000000002</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-79.03449</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7801,20 +9189,30 @@
           <t>ECOLOGICA CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G142" t="n">
-        <v>-8.08595</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-79.01555999999999</v>
-      </c>
-      <c r="I142" t="n">
-        <v>127</v>
-      </c>
-      <c r="J142" t="n">
-        <v>7</v>
-      </c>
-      <c r="K142" t="n">
-        <v>1</v>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-8.08595</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-79.01556</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7853,20 +9251,30 @@
           <t>AUDAX SCIENCE</t>
         </is>
       </c>
-      <c r="G143" t="n">
-        <v>-8.112410000000002</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-79.03354</v>
-      </c>
-      <c r="I143" t="n">
-        <v>89</v>
-      </c>
-      <c r="J143" t="n">
-        <v>15</v>
-      </c>
-      <c r="K143" t="n">
-        <v>1</v>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-8.112410000000002</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-79.03354</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7905,20 +9313,30 @@
           <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
-      <c r="G144" t="n">
-        <v>-8.09418</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-79.0051</v>
-      </c>
-      <c r="I144" t="n">
-        <v>243</v>
-      </c>
-      <c r="J144" t="n">
-        <v>16</v>
-      </c>
-      <c r="K144" t="n">
-        <v>0</v>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-8.09418</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-79.0051</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7957,20 +9375,30 @@
           <t>INNOVA SCHOOLS - TRUJILLO SAN ISIDRO</t>
         </is>
       </c>
-      <c r="G145" t="n">
-        <v>-8.09571</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-79.04545</v>
-      </c>
-      <c r="I145" t="n">
-        <v>774</v>
-      </c>
-      <c r="J145" t="n">
-        <v>29</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0</v>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-8.09571</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-79.04545</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -8009,20 +9437,30 @@
           <t>AI APAEC</t>
         </is>
       </c>
-      <c r="G146" t="n">
-        <v>-8.10891</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-79.00324000000001</v>
-      </c>
-      <c r="I146" t="n">
-        <v>478</v>
-      </c>
-      <c r="J146" t="n">
-        <v>38</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-8.10891</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-79.00324</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -8061,20 +9499,30 @@
           <t>COLEGIO DE CIENCIAS CEPAE</t>
         </is>
       </c>
-      <c r="G147" t="n">
-        <v>-8.09521</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-79.04528000000001</v>
-      </c>
-      <c r="I147" t="n">
-        <v>397</v>
-      </c>
-      <c r="J147" t="n">
-        <v>16</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-8.09521</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-79.04528</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -8113,20 +9561,30 @@
           <t>JUAN PABLO II</t>
         </is>
       </c>
-      <c r="G148" t="n">
-        <v>-8.09812</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-79.04136</v>
-      </c>
-      <c r="I148" t="n">
-        <v>875</v>
-      </c>
-      <c r="J148" t="n">
-        <v>46</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-8.09812</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-79.04136</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -8165,20 +9623,30 @@
           <t>JHON D'ALEMBERT</t>
         </is>
       </c>
-      <c r="G149" t="n">
-        <v>-8.110580000000002</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-79.03994</v>
-      </c>
-      <c r="I149" t="n">
-        <v>223</v>
-      </c>
-      <c r="J149" t="n">
-        <v>31</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0</v>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-8.110580000000002</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-79.03994</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>249519</t>
+          <t>657932</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>206 SABER Y FANTASIA CON MARIA</t>
+          <t>QUIPUS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.10163</t>
+          <t>-8.08804</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.01118</t>
+          <t>-79.00192</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>249524</t>
+          <t>828967</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>207 ALFREDO PINILLOS GOICOCHEA</t>
+          <t>KINDERHOUSE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.10787</t>
+          <t>-8.171478</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.01937</t>
+          <t>-79.008951</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>249543</t>
+          <t>249519</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>209 SANTA ANA</t>
+          <t>206 SABER Y FANTASIA CON MARIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.1168</t>
+          <t>-8.10163</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.0271</t>
+          <t>-79.01118</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>249557</t>
+          <t>249755</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>1733 MI MUNDO MARAVILLOSO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.09693</t>
+          <t>-8.124510000000003</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.02016</t>
+          <t>-79.03323</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>249562</t>
+          <t>250348</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>252 NIÑO JESUS</t>
+          <t>82050 HUERTA BELLA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.10784</t>
+          <t>-8.08828</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.01593</t>
+          <t>-79.0011</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>249576</t>
+          <t>251913</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>253 ISABEL HONORIO DE LAZARTE</t>
+          <t>SANTA CLARA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.103120000000002</t>
+          <t>-8.10797</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.00797</t>
+          <t>-79.02731</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>249581</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1564 RADIANTES CAPULLITOS</t>
+          <t>80848 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.09104</t>
+          <t>-8.09174</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.0093</t>
+          <t>-79.07549</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>249755</t>
+          <t>320394</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1733 MI MUNDO MARAVILLOSO</t>
+          <t>ENGELS CLASS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.124510000000003</t>
+          <t>-8.086824</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.03323</t>
+          <t>-79.00284</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>260</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>249802</t>
+          <t>250065</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GUSTAVO RIES</t>
+          <t>81007 MODELO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.10189</t>
+          <t>-8.104905</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.00614</t>
+          <t>-79.0243</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>249524</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>207 ALFREDO PINILLOS GOICOCHEA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.122920000000002</t>
+          <t>-8.10787</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.02488</t>
+          <t>-79.01937</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>249821</t>
+          <t>250310</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>LICEO TRUJILLO</t>
+          <t>210 DULCE VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.09756</t>
+          <t>-8.11656</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.03293</t>
+          <t>-79.02179</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>249821</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>80002 ANTONIO TORRES ARAUJO</t>
+          <t>LICEO TRUJILLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.1211</t>
+          <t>-8.09756</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.02563</t>
+          <t>-79.03293</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>117</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>249840</t>
+          <t>250206</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>80003 ANDRES AVELINO CACERES</t>
+          <t>MARCIAL ACHARAN Y SMITH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.11725</t>
+          <t>-8.10785</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.02449</t>
+          <t>-79.02515</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>119</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>249859</t>
+          <t>255435</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80005 ABRAHAM VALDELOMAR</t>
+          <t>1638 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.114240000000002</t>
+          <t>-8.12387</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.01542</t>
+          <t>-79.0415</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>249878</t>
+          <t>657201</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80008 REPUBLICA DE ARGENTINA</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.10496</t>
+          <t>-8.104</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.00824</t>
+          <t>-79.028939</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>249883</t>
+          <t>249557</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80010 RICARDO PALMA</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.10104</t>
+          <t>-8.09693</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.02131</t>
+          <t>-79.02016</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>249897</t>
+          <t>250414</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80014 JUAN PABLO II</t>
+          <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.108176</t>
+          <t>-8.10909</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.04526</t>
+          <t>-79.03924</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>249915</t>
+          <t>658837</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>80017 ALFREDO TELLO SALAVARRIA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.1054</t>
+          <t>-8.17255</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.04109</t>
+          <t>-79.0064</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>249920</t>
+          <t>249562</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80018 REPUBLICA DE MEXICO</t>
+          <t>252 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.104</t>
+          <t>-8.10784</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.0413</t>
+          <t>-79.01593</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>249939</t>
+          <t>249859</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80019 CIRO ALEGRIA BAZAN</t>
+          <t>80005 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.11425</t>
+          <t>-8.114240000000002</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.00526</t>
+          <t>-79.01542</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>249944</t>
+          <t>250131</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>80077 ALCIDES CARREÑO BLAS</t>
+          <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.11234</t>
+          <t>-8.12324</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.02209</t>
+          <t>-79.03235</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>339</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>249958</t>
+          <t>250391</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80626 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>SANTA MARIA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.09003</t>
+          <t>-8.121840000000002</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.01133</t>
+          <t>-79.01985</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>249963</t>
+          <t>253484</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80865 DANIEL HOYLE</t>
+          <t>80628</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.09549</t>
+          <t>-8.080947</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.015024</t>
+          <t>-79.084854</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>349</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>249977</t>
+          <t>659200</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>80882 JORGE CHAVEZ</t>
+          <t>BILINGUE LOS ANDES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.09287</t>
+          <t>-8.117620000000002</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.99507</t>
+          <t>-79.03293</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>249982</t>
+          <t>814140</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>80892 LOS PINOS</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.12433</t>
+          <t>-8.172303</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.04182</t>
+          <t>-79.008766</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>250008</t>
+          <t>835171</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>81001 REPUBLICA DE PANAMA</t>
+          <t>JAN KOMENSKY</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.117100000000002</t>
+          <t>-8.109514000000003</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.0269</t>
+          <t>-79.002189</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>250013</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81002 JAVIER HERAUD</t>
+          <t>80003 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.1181</t>
+          <t>-8.11725</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.0195</t>
+          <t>-79.02449</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>337</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>250027</t>
+          <t>250032</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>81003 CESAR ABRAHAM VALLEJO MENDOZA</t>
+          <t>81004 LA UNION</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.10813883264305</t>
+          <t>-8.107021</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.015925025085</t>
+          <t>-79.020124</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,27 +2237,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>250032</t>
+          <t>250051</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>81004 LA UNION</t>
+          <t>81006 AMAUTA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.107021</t>
+          <t>-8.1031</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.020124</t>
+          <t>-79.013</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>250046</t>
+          <t>254681</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>81005 JOSE CARLOS MARIATEGUI LA CHIRA</t>
+          <t>81605 SAN ILDEFONSO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.104134</t>
+          <t>-8.080159</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.014445</t>
+          <t>-78.951185</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,27 +2361,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>250051</t>
+          <t>657357</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>81006 AMAUTA</t>
+          <t>SEBASTIAN SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.1031</t>
+          <t>-8.11645</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.013</t>
+          <t>-79.02109</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>250065</t>
+          <t>844552</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>81007 MODELO</t>
+          <t>AUDAX SCIENCE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.104905</t>
+          <t>-8.112410000000002</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.0243</t>
+          <t>-79.03354</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>89</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>250070</t>
+          <t>249944</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81008 / 81008 MUNICIPAL</t>
+          <t>80077 ALCIDES CARREÑO BLAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.10647</t>
+          <t>-8.11234</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.022</t>
+          <t>-79.02209</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>250089</t>
+          <t>250225</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>81010 VIRGEN DE LA PUERTA</t>
+          <t>SAN NICOLAS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.11834</t>
+          <t>-8.109310000000002</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.04434</t>
+          <t>-79.03556</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>250094</t>
+          <t>250490</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>81011 ANTONIO RAYMONDI</t>
+          <t>ALEJANDRO DEUSTUA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.10738</t>
+          <t>-8.11717</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.02935</t>
+          <t>-79.02265</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>250112</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>81015 CARLOS E. UCEDA MEZA</t>
+          <t>MIS ABEJITAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.12436</t>
+          <t>-8.09656</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.0284</t>
+          <t>-79.04158</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>250131</t>
+          <t>251606</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.12324</t>
+          <t>-8.11012</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.03235</t>
+          <t>-79.01557</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>250145</t>
+          <t>251847</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>81746 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>SAN GERARDO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.111660000000002</t>
+          <t>-8.10093</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.04173</t>
+          <t>-79.03815</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>250150</t>
+          <t>252936</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>81755 MEDALLA MILAGROSA</t>
+          <t>SAN ESTEBAN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.09283</t>
+          <t>-8.08833</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.0046</t>
+          <t>-79.01571</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>250206</t>
+          <t>254742</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARCIAL ACHARAN Y SMITH</t>
+          <t>81526 VICTOR GANOZA PLAZA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.10785</t>
+          <t>-8.103</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.02515</t>
+          <t>-78.9121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>292</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>250225</t>
+          <t>846513</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN NICOLAS</t>
+          <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.109310000000002</t>
+          <t>-8.09418</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.03556</t>
+          <t>-79.0051</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>250230</t>
+          <t>858129</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>COLEGIO DE CIENCIAS CEPAE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.11295</t>
+          <t>-8.09521</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.02612</t>
+          <t>-79.04528</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>397</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>250249</t>
+          <t>249543</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VICTOR ANDRES BELAUNDE</t>
+          <t>209 SANTA ANA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.106057</t>
+          <t>-8.1168</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.023275</t>
+          <t>-79.0271</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>250268</t>
+          <t>249581</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CECAT MARCIAL ACHARAN</t>
+          <t>1564 RADIANTES CAPULLITOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.12433</t>
+          <t>-8.09104</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.02456</t>
+          <t>-79.0093</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>423</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>250310</t>
+          <t>250145</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>210 DULCE VIRGEN DE FATIMA</t>
+          <t>81746 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.11656</t>
+          <t>-8.111660000000002</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.02179</t>
+          <t>-79.04173</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>290</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>250334</t>
+          <t>825191</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MARIANO SANTOS MATEO</t>
+          <t>AI APAEC TRUJILLO CENTRO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.09545</t>
+          <t>-8.11282</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.04459</t>
+          <t>-79.03315</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>250348</t>
+          <t>249576</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>82050 HUERTA BELLA</t>
+          <t>253 ISABEL HONORIO DE LAZARTE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.08828</t>
+          <t>-8.103120000000002</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.0011</t>
+          <t>-79.00797</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>250353</t>
+          <t>249939</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MARIA NEGRON UGARTE</t>
+          <t>80019 CIRO ALEGRIA BAZAN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.10709</t>
+          <t>-8.11425</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.00709</t>
+          <t>-79.00526</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>250372</t>
+          <t>712896</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DANTE ALIGHIERI</t>
+          <t>TYCHO BRAHE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.12272</t>
+          <t>-8.09599</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.02269</t>
+          <t>-79.02454</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>271</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>250386</t>
+          <t>825214</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>ORION BEN CARSON</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.118650000000002</t>
+          <t>-8.09925</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.03451</t>
+          <t>-79.0281</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>283</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>250391</t>
+          <t>249897</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE GUADALUPE</t>
+          <t>80014 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.121840000000002</t>
+          <t>-8.108176</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.01985</t>
+          <t>-79.04526</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>496</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>250409</t>
+          <t>250089</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LA ASUNCION</t>
+          <t>81010 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.10451</t>
+          <t>-8.11834</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.03596</t>
+          <t>-79.04434</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>404</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>250414</t>
+          <t>250999</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA</t>
+          <t>LAS CAPULLANAS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.10909</t>
+          <t>-8.109920000000002</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.03924</t>
+          <t>-79.04155</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>250428</t>
+          <t>254643</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>80869 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-8.11348</t>
+          <t>-8.125003</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-79.02592</t>
+          <t>-78.949009</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>359</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>250471</t>
+          <t>255727</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ADVENTISTA JOSE DE SAN MARTIN</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.106696</t>
+          <t>-8.131</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-79.025382</t>
+          <t>-79.04408</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>425</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>250490</t>
+          <t>557800</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ALEJANDRO DEUSTUA</t>
+          <t>KEPLER</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.11717</t>
+          <t>-8.11345</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-79.02265</t>
+          <t>-79.03152</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,37 +4035,37 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>250598</t>
+          <t>659827</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KINDERLAND</t>
+          <t>JAN KOMENSKY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.12466</t>
+          <t>-8.107570000000003</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-79.02916</t>
+          <t>-79.00779</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>321</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>250635</t>
+          <t>660053</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS SCHOOL</t>
+          <t>SIGNOS DE FE LA SALLE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-8.092980000000003</t>
+          <t>-8.09189</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-79.01129</t>
+          <t>-79.04648</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>250758</t>
+          <t>657418</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EIFFEL SCHOOLS</t>
+          <t>FRAY MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-8.109870000000003</t>
+          <t>-8.09166</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-79.00984</t>
+          <t>-79.00578</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>250819</t>
+          <t>657606</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>NUESTRA SEÑORA DE SCHOENSTATT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-8.121560000000002</t>
+          <t>-8.12233</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-79.03678</t>
+          <t>-79.03555</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>343</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>250999</t>
+          <t>700011</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LAS CAPULLANAS</t>
+          <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-8.109920000000002</t>
+          <t>-8.12903</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-79.04155</t>
+          <t>-79.02064</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>251102</t>
+          <t>833214</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>GRACIELA DIAZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-8.10272</t>
+          <t>-8.102481</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-79.03378</t>
+          <t>-79.005257</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>251116</t>
+          <t>250046</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>81005 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-8.11811</t>
+          <t>-8.104134</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-79.04256</t>
+          <t>-79.014445</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,32 +4469,32 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>251277</t>
+          <t>252248</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MIS ABEJITAS</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-8.09656</t>
+          <t>-8.11863</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-79.04158</t>
+          <t>-79.02393</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>351</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>831601</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MARIA MADRE</t>
+          <t>NOBEL SCHOOL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-8.08887</t>
+          <t>-8.11101</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-79.02103</t>
+          <t>-79.03515</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>251437</t>
+          <t>837373</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>PORTAL DE BELEN</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-8.09522</t>
+          <t>-8.102370000000002</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-79.01618</t>
+          <t>-79.03449</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>251606</t>
+          <t>249920</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>80018 REPUBLICA DE MEXICO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-8.11012</t>
+          <t>-8.104</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-79.01557</t>
+          <t>-79.0413</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>560</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>251753</t>
+          <t>252074</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SIR ALEXANDER FLEMING</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-8.12655</t>
+          <t>-8.09733</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-79.03494</t>
+          <t>-79.0183</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>251772</t>
+          <t>254737</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TALENTOS</t>
+          <t>81523 JOSE IGNACIO CHOPITEA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-8.13195</t>
+          <t>-8.088100000000003</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-79.02874</t>
+          <t>-78.9691</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>428</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>251828</t>
+          <t>741238</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WILLIAM HARVEY</t>
+          <t>LOUIS PASTEUR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-8.12216</t>
+          <t>-8.09229</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-79.04248</t>
+          <t>-78.9574</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>547</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>251847</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SAN GERARDO</t>
+          <t>PERUANO AMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-8.10093</t>
+          <t>-8.1068</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-79.03815</t>
+          <t>-79.03232</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>562</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,37 +4965,37 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>251913</t>
+          <t>639194</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SANTA CLARA</t>
+          <t>SANTA TERESITA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-8.10797</t>
+          <t>-8.08729</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-79.02731</t>
+          <t>-79.01659</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>333</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>251951</t>
+          <t>250428</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HERMANOS BLANCO</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-8.09752</t>
+          <t>-8.11348</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-79.03629</t>
+          <t>-79.02592</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>251994</t>
+          <t>749970</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UNIVERSAL SCHOOL</t>
+          <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-8.122</t>
+          <t>-8.12073</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-79.02307</t>
+          <t>-79.01998</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>245</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>815385</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>FUTURA SCHOOLS - SEDE SAN ISIDRO</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-8.103440000000003</t>
+          <t>-8.09522</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-79.03421</t>
+          <t>-79.05383</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>495</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>252045</t>
+          <t>831899</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAN CARLOS Y SAN MARCELO</t>
+          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-8.10816</t>
+          <t>-8.10006</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-79.02894</t>
+          <t>-79.03645</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>668</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>252074</t>
+          <t>250471</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>ADVENTISTA JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-8.09733</t>
+          <t>-8.106696</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-79.0183</t>
+          <t>-79.025382</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>252106</t>
+          <t>250635</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-8.0954</t>
+          <t>-8.092980000000003</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-79.01109</t>
+          <t>-79.01129</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>244</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>252125</t>
+          <t>251116</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RAFAEL NARVAEZ CADENILLAS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-8.11777</t>
+          <t>-8.11811</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-79.04216</t>
+          <t>-79.04256</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5461,37 +5461,37 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>252210</t>
+          <t>657300</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-8.124090000000002</t>
+          <t>-8.102393</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-79.02226</t>
+          <t>-79.005064</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>410</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>252234</t>
+          <t>657338</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>MAYOR DE SAN MARCOS</t>
+          <t>INTEGRAL CLASS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-8.11657</t>
+          <t>-8.11736</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-79.02464</t>
+          <t>-79.03386</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>447</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>252248</t>
+          <t>658823</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-8.11863</t>
+          <t>-8.09474</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-79.02393</t>
+          <t>-79.00501</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,37 +5647,37 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>252795</t>
+          <t>658903</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>80824 JOSE CARLOS MARIATEGUI</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-8.08649</t>
+          <t>-8.101760000000002</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-79.00268</t>
+          <t>-79.03523</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>346</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>252936</t>
+          <t>836566</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAN ESTEBAN</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-8.08833</t>
+          <t>-8.09687</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-79.01571</t>
+          <t>-79.02194</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>253436</t>
+          <t>249958</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>80033 JOSE OLAYA BALANDRA</t>
+          <t>80626 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-8.081</t>
+          <t>-8.09003</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-79.11715</t>
+          <t>-79.01133</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>253484</t>
+          <t>254921</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>80048 JOSE EULOGIO GARRIDO</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-8.080947</t>
+          <t>-8.147622</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-79.084854</t>
+          <t>-79.004128</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>675</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>668638</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>80848 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>MONTEVERDE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-8.09174</t>
+          <t>-8.09207</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-79.07549</t>
+          <t>-79.04213</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>303</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>254643</t>
+          <t>811448</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>80869 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>INNOVA SCHOOLS - TRUJILLO</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-8.125003</t>
+          <t>-8.134278</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-78.949009</t>
+          <t>-79.025868</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>977</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>254681</t>
+          <t>831903</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>81605 SAN ILDEFONSO</t>
+          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-8.080159</t>
+          <t>-8.09717</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-78.951185</t>
+          <t>-79.03602</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>626</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>254737</t>
+          <t>855183</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>81523 JOSE IGNACIO CHOPITEA</t>
+          <t>INNOVA SCHOOLS - TRUJILLO SAN ISIDRO</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-8.088100000000003</t>
+          <t>-8.09571</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-78.9691</t>
+          <t>-79.04545</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>774</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>254742</t>
+          <t>250598</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>81526 VICTOR GANOZA PLAZA</t>
+          <t>KINDERLAND</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-8.103</t>
+          <t>-8.12466</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-78.9121</t>
+          <t>-79.02916</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>254902</t>
+          <t>250070</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1721 LINA SKRABONJA</t>
+          <t>81008 / 81008 MUNICIPAL</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-8.16952</t>
+          <t>-8.10647</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-79.01059</t>
+          <t>-79.022</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>254921</t>
+          <t>250150</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>80048 JOSE EULOGIO GARRIDO</t>
+          <t>81755 MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-8.147622</t>
+          <t>-8.09283</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-79.004128</t>
+          <t>-79.0046</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>558</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>294446</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>JOSE EMILIO LEFEBVRE FRANCOEUR</t>
+          <t>80006 NUEVO PERU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-8.1725</t>
+          <t>-8.106030000000002</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-79.00904</t>
+          <t>-79.01125</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>763</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>255435</t>
+          <t>864192</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1638 PASITOS DE JESUS</t>
+          <t>JHON D'ALEMBERT</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-8.12387</t>
+          <t>-8.110580000000002</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-79.0415</t>
+          <t>-79.03994</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>255727</t>
+          <t>540353</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>HANS HEINRICH BRUNING</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-8.131</t>
+          <t>-8.12683</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-79.04408</t>
+          <t>-79.02998</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>564</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>255732</t>
+          <t>250758</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CLARETIANO</t>
+          <t>EIFFEL SCHOOLS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-8.12918</t>
+          <t>-8.109870000000003</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-79.03632</t>
+          <t>-79.00984</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>601</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>294446</t>
+          <t>251362</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>80006 NUEVO PERU</t>
+          <t>MARIA MADRE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-8.106030000000002</t>
+          <t>-8.08887</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-79.01125</t>
+          <t>-79.02103</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>752</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>320394</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>ENGELS CLASS</t>
+          <t>WILLIAM HARVEY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-8.086824</t>
+          <t>-8.12216</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-79.00284</t>
+          <t>-79.04248</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>419</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>532918</t>
+          <t>252234</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO ABRAHAM LINCOLN</t>
+          <t>MAYOR DE SAN MARCOS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-8.1068</t>
+          <t>-8.11657</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-79.03232</t>
+          <t>-79.02464</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>503</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>540353</t>
+          <t>824479</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>HANS HEINRICH BRUNING</t>
+          <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-8.12683</t>
+          <t>-8.10614</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-79.02998</t>
+          <t>-79.024557</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>580</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>557800</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>KEPLER</t>
+          <t>80882 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-8.11345</t>
+          <t>-8.09287</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-79.03152</t>
+          <t>-78.99507</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>668</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>639194</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SANTA TERESITA</t>
+          <t>80017 ALFREDO TELLO SALAVARRIA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-8.08729</t>
+          <t>-8.1054</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-79.01659</t>
+          <t>-79.04109</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>657201</t>
+          <t>250249</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-8.104</t>
+          <t>-8.106057</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-79.028939</t>
+          <t>-79.023275</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>553</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>657300</t>
+          <t>250334</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-8.102393</t>
+          <t>-8.09545</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-79.005064</t>
+          <t>-79.04459</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>657338</t>
+          <t>252106</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>INTEGRAL CLASS</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-8.11736</t>
+          <t>-8.0954</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-79.03386</t>
+          <t>-79.01109</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>748</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>657357</t>
+          <t>250268</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SEBASTIAN SALAZAR BONDY</t>
+          <t>CECAT MARCIAL ACHARAN</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-8.11645</t>
+          <t>-8.12433</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-79.02109</t>
+          <t>-79.02456</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>623</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>657418</t>
+          <t>250819</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FRAY MARTIN DE PORRES</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-8.09166</t>
+          <t>-8.121560000000002</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-79.00578</t>
+          <t>-79.03678</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>656</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>657606</t>
+          <t>857714</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE SCHOENSTATT</t>
+          <t>AI APAEC</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-8.12233</t>
+          <t>-8.10891</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-79.03555</t>
+          <t>-79.00324</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>478</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,37 +7321,37 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>657932</t>
+          <t>252045</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>QUIPUS</t>
+          <t>SAN CARLOS Y SAN MARCELO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-8.08804</t>
+          <t>-8.10816</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-79.00192</t>
+          <t>-79.02894</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>658205</t>
+          <t>716875</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>DESPERTAR</t>
+          <t>EL CULTURAL AMERICAN SCHOOL</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-8.099410000000002</t>
+          <t>-8.11726</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-79.03782</t>
+          <t>-79.03255</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>539</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>658823</t>
+          <t>250112</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SAN JOSE SCHOOL</t>
+          <t>81015 CARLOS E. UCEDA MEZA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-8.09474</t>
+          <t>-8.12436</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-79.00501</t>
+          <t>-79.0284</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>802</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>658837</t>
+          <t>255039</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>JOSE EMILIO LEFEBVRE FRANCOEUR</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-8.17255</t>
+          <t>-8.1725</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-79.0064</t>
+          <t>-79.00904</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>658903</t>
+          <t>250094</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>81011 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-8.101760000000002</t>
+          <t>-8.10738</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-79.03523</t>
+          <t>-79.02935</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>962</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,37 +7631,37 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>659200</t>
+          <t>253436</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>BILINGUE LOS ANDES</t>
+          <t>80033 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-8.117620000000002</t>
+          <t>-8.081</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-79.03293</t>
+          <t>-79.11715</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>659827</t>
+          <t>861301</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JAN KOMENSKY</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-8.107570000000003</t>
+          <t>-8.09812</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-79.00779</t>
+          <t>-79.04136</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>875</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>660053</t>
+          <t>249982</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SIGNOS DE FE LA SALLE</t>
+          <t>80892 LOS PINOS</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-8.09189</t>
+          <t>-8.12433</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-79.04648</t>
+          <t>-79.04182</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>668638</t>
+          <t>251951</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MONTEVERDE</t>
+          <t>HERMANOS BLANCO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-8.09207</t>
+          <t>-8.09752</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-79.04213</t>
+          <t>-79.03629</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>833</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>700011</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA MARIA</t>
+          <t>DANTE ALIGHIERI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-8.12903</t>
+          <t>-8.12272</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-79.02064</t>
+          <t>-79.02269</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>712896</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TYCHO BRAHE</t>
+          <t>80002 ANTONIO TORRES ARAUJO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-8.09599</t>
+          <t>-8.1211</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-79.02454</t>
+          <t>-79.02563</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -8003,42 +8003,42 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>716875</t>
+          <t>251772</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>EL CULTURAL AMERICAN SCHOOL</t>
+          <t>TALENTOS</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-8.11726</t>
+          <t>-8.13195</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-79.03255</t>
+          <t>-79.02874</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>812</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>741238</t>
+          <t>249883</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LOUIS PASTEUR</t>
+          <t>80010 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-8.09229</t>
+          <t>-8.10104</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-78.9574</t>
+          <t>-79.02131</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>744251</t>
+          <t>250027</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>81014 PEDRO MERCEDES UREÑA</t>
+          <t>81003 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-8.11221643601271</t>
+          <t>-8.10813883264305</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-79.0487275389903</t>
+          <t>-79.015925025085</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>749970</t>
+          <t>250008</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA MARIA</t>
+          <t>81001 REPUBLICA DE PANAMA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-8.12073</t>
+          <t>-8.117100000000002</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-79.01998</t>
+          <t>-79.0269</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>811448</t>
+          <t>831795</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO</t>
+          <t>INNOVA SCHOOLS - TRUJILLO SANTA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-8.134278</t>
+          <t>-8.0951</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-79.025868</t>
+          <t>-79.01537</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>814140</t>
+          <t>249963</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>80865 DANIEL HOYLE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-8.172303</t>
+          <t>-8.09549</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-79.008766</t>
+          <t>-79.015024</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8375,12 +8375,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>815385</t>
+          <t>251437</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS - SEDE SAN ISIDRO</t>
+          <t>PORTAL DE BELEN</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8390,17 +8390,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-79.05383</t>
+          <t>-79.01618</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>824479</t>
+          <t>252012</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ALEXANDER GRAHAM BELL</t>
+          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-8.10614</t>
+          <t>-8.103440000000003</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-79.024557</t>
+          <t>-79.03421</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,37 +8499,37 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>825191</t>
+          <t>251994</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AI APAEC TRUJILLO CENTRO</t>
+          <t>UNIVERSAL SCHOOL</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-8.11282</t>
+          <t>-8.122</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-79.03315</t>
+          <t>-79.02307</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8561,37 +8561,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>825214</t>
+          <t>844279</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ORION BEN CARSON</t>
+          <t>ECOLOGICA CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-8.09925</t>
+          <t>-8.08595</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-79.0281</t>
+          <t>-79.01556</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>127</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>828967</t>
+          <t>250013</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KINDERHOUSE</t>
+          <t>81002 JAVIER HERAUD</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-8.171478</t>
+          <t>-8.1181</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-79.008951</t>
+          <t>-79.0195</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8685,37 +8685,37 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>831601</t>
+          <t>250409</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NOBEL SCHOOL</t>
+          <t>LA ASUNCION</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-8.11101</t>
+          <t>-8.10451</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-79.03515</t>
+          <t>-79.03596</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>831795</t>
+          <t>250386</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO SANTA</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-8.0951</t>
+          <t>-8.118650000000002</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-79.01537</t>
+          <t>-79.03451</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>831899</t>
+          <t>249878</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
+          <t>80008 REPUBLICA DE ARGENTINA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-8.10006</t>
+          <t>-8.10496</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-79.03645</t>
+          <t>-79.00824</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>831903</t>
+          <t>251753</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
+          <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-8.09717</t>
+          <t>-8.12655</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-79.03602</t>
+          <t>-79.03494</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>641</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8933,37 +8933,37 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>252210</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>GRACIELA DIAZ</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-8.102481</t>
+          <t>-8.124090000000002</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-79.005257</t>
+          <t>-79.02226</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8995,37 +8995,37 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>835171</t>
+          <t>658205</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JAN KOMENSKY</t>
+          <t>DESPERTAR</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-8.109514000000003</t>
+          <t>-8.099410000000002</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-79.002189</t>
+          <t>-79.03782</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>836566</t>
+          <t>255732</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>CLARETIANO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-8.09687</t>
+          <t>-8.12918</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-79.02194</t>
+          <t>-79.03632</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>837373</t>
+          <t>250353</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>MARIA NEGRON UGARTE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-8.102370000000002</t>
+          <t>-8.10709</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-79.03449</t>
+          <t>-79.00709</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9181,37 +9181,37 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>844279</t>
+          <t>249802</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>ECOLOGICA CESAR VALLEJO</t>
+          <t>GUSTAVO RIES</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-8.08595</t>
+          <t>-8.10189</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-79.01556</t>
+          <t>-79.00614</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>87</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9243,37 +9243,37 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>844552</t>
+          <t>251102</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AUDAX SCIENCE</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-8.112410000000002</t>
+          <t>-8.10272</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-79.03354</t>
+          <t>-79.03378</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>846513</t>
+          <t>254902</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SAN JOSE SCHOOL</t>
+          <t>1721 LINA SKRABONJA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-8.09418</t>
+          <t>-8.16952</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-79.0051</t>
+          <t>-79.01059</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>855183</t>
+          <t>252125</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO SAN ISIDRO</t>
+          <t>RAFAEL NARVAEZ CADENILLAS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-8.09571</t>
+          <t>-8.11777</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-79.04545</t>
+          <t>-79.04216</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>857714</t>
+          <t>744251</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AI APAEC</t>
+          <t>81014 PEDRO MERCEDES UREÑA</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-8.10891</t>
+          <t>-8.11221643601271</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-79.00324</t>
+          <t>-79.0487275389903</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -9491,37 +9491,37 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>858129</t>
+          <t>252795</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS CEPAE</t>
+          <t>80824 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-8.09521</t>
+          <t>-8.08649</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-79.04528</t>
+          <t>-79.00268</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>861301</t>
+          <t>249816</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-8.09812</t>
+          <t>-8.122920000000002</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-79.04136</t>
+          <t>-79.02488</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>95</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9615,32 +9615,32 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>864192</t>
+          <t>250230</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JHON D'ALEMBERT</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-8.110580000000002</t>
+          <t>-8.11295</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-79.03994</t>
+          <t>-79.02612</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.124510000000003</t>
+          <t>-8.12451</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.114240000000002</t>
+          <t>-8.11424</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.121840000000002</t>
+          <t>-8.12184</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.117620000000002</t>
+          <t>-8.11762</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.109514000000003</t>
+          <t>-8.109514</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.112410000000002</t>
+          <t>-8.11241</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.109310000000002</t>
+          <t>-8.10931</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.111660000000002</t>
+          <t>-8.11166</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.103120000000002</t>
+          <t>-8.10312</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.109920000000002</t>
+          <t>-8.10992</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.107570000000003</t>
+          <t>-8.10757</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-8.102370000000002</t>
+          <t>-8.10237</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-8.088100000000003</t>
+          <t>-8.0881</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-8.092980000000003</t>
+          <t>-8.09298</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-8.101760000000002</t>
+          <t>-8.10176</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-8.106030000000002</t>
+          <t>-8.10603</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-8.110580000000002</t>
+          <t>-8.11058</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-8.109870000000003</t>
+          <t>-8.10987</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-8.121560000000002</t>
+          <t>-8.12156</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-8.117100000000002</t>
+          <t>-8.1171</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-8.103440000000003</t>
+          <t>-8.10344</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-8.118650000000002</t>
+          <t>-8.11865</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-8.124090000000002</t>
+          <t>-8.12409</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-8.099410000000002</t>
+          <t>-8.09941</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-8.122920000000002</t>
+          <t>-8.12292</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>657932</t>
+          <t>864192</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>QUIPUS</t>
+          <t>JHON D'ALEMBERT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.08804</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.00192</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.110580000000002</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79.03994</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>828967</t>
+          <t>861301</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>KINDERHOUSE</t>
+          <t>JUAN PABLO II</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.171478</t>
+          <t>875</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.008951</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-8.09812</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-79.04136</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>249519</t>
+          <t>858129</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>206 SABER Y FANTASIA CON MARIA</t>
+          <t>COLEGIO DE CIENCIAS CEPAE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.10163</t>
+          <t>397</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.01118</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>-8.09521</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.04528</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>249755</t>
+          <t>857714</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1733 MI MUNDO MARAVILLOSO</t>
+          <t>AI APAEC</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.12451</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.03323</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-8.10891</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.00324</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>250348</t>
+          <t>855183</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>82050 HUERTA BELLA</t>
+          <t>INNOVA SCHOOLS - TRUJILLO SAN ISIDRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.08828</t>
+          <t>774</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.0011</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-8.09571</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.04545</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,37 +811,37 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>251913</t>
+          <t>846513</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SANTA CLARA</t>
+          <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.10797</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.02731</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-8.09418</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.0051</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>844552</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>80848 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>AUDAX SCIENCE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.09174</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.07549</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-8.112410000000002</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.03354</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>320394</t>
+          <t>844279</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENGELS CLASS</t>
+          <t>ECOLOGICA CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.086824</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.00284</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>-8.08595</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.01556</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>250065</t>
+          <t>837373</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81007 MODELO</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.104905</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.0243</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>-8.102370000000002</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>-79.03449</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>249524</t>
+          <t>836566</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>207 ALFREDO PINILLOS GOICOCHEA</t>
+          <t>SAN PEDRO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.10787</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.01937</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-8.09687</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.02194</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>250310</t>
+          <t>835171</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>210 DULCE VIRGEN DE FATIMA</t>
+          <t>JAN KOMENSKY</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.11656</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.02179</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-8.109514000000003</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.002189</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>249821</t>
+          <t>833214</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LICEO TRUJILLO</t>
+          <t>GRACIELA DIAZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.09756</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.03293</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2462</t>
+          <t>-8.102481</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>-79.005257</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>250206</t>
+          <t>831903</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARCIAL ACHARAN Y SMITH</t>
+          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.10785</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.02515</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>-8.09717</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>-79.03602</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>255435</t>
+          <t>831899</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1638 PASITOS DE JESUS</t>
+          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.12387</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.0415</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-8.10006</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-79.03645</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>657201</t>
+          <t>831795</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>INNOVA SCHOOLS - TRUJILLO SANTA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.104</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.028939</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>-8.0951</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-79.01537</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>249557</t>
+          <t>831601</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>NOBEL SCHOOL</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.09693</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.02016</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>-8.11101</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.03515</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>250414</t>
+          <t>828967</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA MAGDALENA SOFIA</t>
+          <t>KINDERHOUSE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.10909</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.03924</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>-8.171478</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.008951</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>658837</t>
+          <t>825214</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN CARLOS</t>
+          <t>ORION BEN CARSON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.17255</t>
+          <t>283</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.0064</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-8.09925</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.0281</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>249562</t>
+          <t>825191</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>252 NIÑO JESUS</t>
+          <t>AI APAEC TRUJILLO CENTRO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.10784</t>
+          <t>331</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.01593</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-8.11282</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.03315</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>249859</t>
+          <t>824479</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80005 ABRAHAM VALDELOMAR</t>
+          <t>ALEXANDER GRAHAM BELL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.11424</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.01542</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-8.10614</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.024557</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>250131</t>
+          <t>815385</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
+          <t>FUTURA SCHOOLS - SEDE SAN ISIDRO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.12324</t>
+          <t>495</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.03235</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>-8.09522</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.05383</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>250391</t>
+          <t>814140</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE GUADALUPE</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.12184</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.01985</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-8.172303</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.008766</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>253484</t>
+          <t>811448</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>INNOVA SCHOOLS - TRUJILLO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.080947</t>
+          <t>977</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.084854</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>-8.134278</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.025868</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>659200</t>
+          <t>749970</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BILINGUE LOS ANDES</t>
+          <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.11762</t>
+          <t>245</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.03293</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>-8.12073</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.01998</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>814140</t>
+          <t>744251</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>81014 PEDRO MERCEDES UREÑA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.172303</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.008766</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-8.11221643601271</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.0487275389903</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>835171</t>
+          <t>741238</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JAN KOMENSKY</t>
+          <t>LOUIS PASTEUR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.109514</t>
+          <t>547</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.002189</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-8.09229</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.9574</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>249840</t>
+          <t>716875</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>80003 ANDRES AVELINO CACERES</t>
+          <t>EL CULTURAL AMERICAN SCHOOL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.11725</t>
+          <t>539</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.02449</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>-8.11726</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.03255</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>250032</t>
+          <t>712896</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>81004 LA UNION</t>
+          <t>TYCHO BRAHE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.107021</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.020124</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-8.09599</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.02454</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>250051</t>
+          <t>700011</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>81006 AMAUTA</t>
+          <t>TRILCE DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.1031</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.013</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-8.12903</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.02064</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>254681</t>
+          <t>668638</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>81605 SAN ILDEFONSO</t>
+          <t>MONTEVERDE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.080159</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.951185</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-8.09207</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.04213</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>657357</t>
+          <t>660053</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SEBASTIAN SALAZAR BONDY</t>
+          <t>SIGNOS DE FE LA SALLE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.11645</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.02109</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-8.09189</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.04648</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>844552</t>
+          <t>659827</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AUDAX SCIENCE</t>
+          <t>JAN KOMENSKY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.11241</t>
+          <t>321</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.03354</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>-8.107570000000003</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-79.00779</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>249944</t>
+          <t>659200</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>80077 ALCIDES CARREÑO BLAS</t>
+          <t>BILINGUE LOS ANDES</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.11234</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.02209</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-8.117620000000002</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.03293</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>250225</t>
+          <t>658903</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SAN NICOLAS</t>
+          <t>TRILCE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.10931</t>
+          <t>346</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.03556</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-8.101760000000002</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.03523</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>250490</t>
+          <t>658837</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ALEJANDRO DEUSTUA</t>
+          <t>SAN CARLOS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.11717</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.02265</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-8.17255</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.0064</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>251277</t>
+          <t>658823</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MIS ABEJITAS</t>
+          <t>SAN JOSE SCHOOL</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.09656</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.04158</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-8.09474</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.00501</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>251606</t>
+          <t>658205</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE PORRES</t>
+          <t>DESPERTAR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.11012</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.01557</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-8.099410000000002</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.03782</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,37 +2795,37 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>251847</t>
+          <t>657932</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN GERARDO</t>
+          <t>QUIPUS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.10093</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.03815</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.08804</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.00192</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>252936</t>
+          <t>657606</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN ESTEBAN</t>
+          <t>NUESTRA SEÑORA DE SCHOENSTATT</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.08833</t>
+          <t>343</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.01571</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>-8.12233</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.03555</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>254742</t>
+          <t>657418</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>81526 VICTOR GANOZA PLAZA</t>
+          <t>FRAY MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.103</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.9121</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>-8.09166</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.00578</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>846513</t>
+          <t>657357</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SAN JOSE SCHOOL</t>
+          <t>SEBASTIAN SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.09418</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.0051</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-8.11645</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.02109</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>858129</t>
+          <t>657338</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS CEPAE</t>
+          <t>INTEGRAL CLASS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.09521</t>
+          <t>447</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.04528</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>-8.11736</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.03386</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>249543</t>
+          <t>657300</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>209 SANTA ANA</t>
+          <t>INMACULADA VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.1168</t>
+          <t>410</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.0271</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-8.102393</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.005064</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>249581</t>
+          <t>657201</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1564 RADIANTES CAPULLITOS</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.09104</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.0093</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>-8.104</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.028939</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>250145</t>
+          <t>639194</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>81746 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>SANTA TERESITA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.11166</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.04173</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>-8.08729</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.01659</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>825191</t>
+          <t>557800</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AI APAEC TRUJILLO CENTRO</t>
+          <t>KEPLER</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.11282</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.03315</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>-8.11345</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.03152</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>249576</t>
+          <t>540353</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>253 ISABEL HONORIO DE LAZARTE</t>
+          <t>HANS HEINRICH BRUNING</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.10312</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.00797</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>-8.12683</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.02998</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>249939</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>80019 CIRO ALEGRIA BAZAN</t>
+          <t>PERUANO AMERICANO ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.11425</t>
+          <t>562</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.00526</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-8.1068</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.03232</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,37 +3477,37 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>250367</t>
+          <t>320394</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>81584 EVERARDO ZAPATA SANTILLANA</t>
+          <t>ENGELS CLASS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.09984</t>
+          <t>260</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-79.04849</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-8.086824</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.00284</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>712896</t>
+          <t>294446</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TYCHO BRAHE</t>
+          <t>80006 NUEVO PERU</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.09599</t>
+          <t>763</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.02454</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-8.106030000000002</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.01125</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>825214</t>
+          <t>255732</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ORION BEN CARSON</t>
+          <t>CLARETIANO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.09925</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.0281</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>-8.12918</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.03632</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>249897</t>
+          <t>255727</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>80014 JUAN PABLO II</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.108176</t>
+          <t>425</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.04526</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>-8.131</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.04408</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>250089</t>
+          <t>255435</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>81010 VIRGEN DE LA PUERTA</t>
+          <t>1638 PASITOS DE JESUS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.11834</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.04434</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>-8.12387</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.0415</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>250999</t>
+          <t>255039</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>LAS CAPULLANAS</t>
+          <t>JOSE EMILIO LEFEBVRE FRANCOEUR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.10992</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.04155</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-8.1725</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.00904</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>254643</t>
+          <t>254921</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>80869 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
+          <t>80048 JOSE EULOGIO GARRIDO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-8.125003</t>
+          <t>675</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-78.949009</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>-8.147622</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.004128</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>255727</t>
+          <t>254902</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>1721 LINA SKRABONJA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-8.131</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-79.04408</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>-8.16952</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.01059</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>557800</t>
+          <t>254742</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KEPLER</t>
+          <t>81526 VICTOR GANOZA PLAZA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-8.11345</t>
+          <t>292</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-79.03152</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-8.103</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.9121</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,32 +4035,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>659827</t>
+          <t>254737</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JAN KOMENSKY</t>
+          <t>81523 JOSE IGNACIO CHOPITEA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-8.10757</t>
+          <t>428</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-79.00779</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>-8.088100000000003</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.9691</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>660053</t>
+          <t>254681</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SIGNOS DE FE LA SALLE</t>
+          <t>81605 SAN ILDEFONSO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-8.09189</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-79.04648</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-8.080159</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.951185</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>657418</t>
+          <t>254643</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FRAY MARTIN DE PORRES</t>
+          <t>80869 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-8.09166</t>
+          <t>359</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-79.00578</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-8.125003</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-78.949009</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>657606</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE SCHOENSTATT</t>
+          <t>80848 NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-8.12233</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-79.03555</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>-8.09174</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.07549</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>700011</t>
+          <t>253484</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA MARIA</t>
+          <t>80628</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-8.12903</t>
+          <t>349</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-79.02064</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>-8.080947</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.084854</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>833214</t>
+          <t>253436</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>GRACIELA DIAZ</t>
+          <t>80033 JOSE OLAYA BALANDRA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-8.102481</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-79.005257</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-8.081</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.11715</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>250046</t>
+          <t>252936</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>81005 JOSE CARLOS MARIATEGUI LA CHIRA</t>
+          <t>SAN ESTEBAN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-8.104134</t>
+          <t>355</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-79.014445</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-8.08833</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.01571</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>252248</t>
+          <t>252795</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SAN FELIPE</t>
+          <t>80824 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-8.11863</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-79.02393</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>-8.08649</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.00268</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>831601</t>
+          <t>252248</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NOBEL SCHOOL</t>
+          <t>SAN FELIPE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-8.11101</t>
+          <t>351</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-79.03515</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-8.11863</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.02393</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>837373</t>
+          <t>252234</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>MAYOR DE SAN MARCOS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-8.10237</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-79.03449</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-8.11657</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.02464</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,37 +4655,37 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>249920</t>
+          <t>252210</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>80018 REPUBLICA DE MEXICO</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-8.104</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-79.0413</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>-8.124090000000002</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.02226</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>252074</t>
+          <t>252125</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAN LUIS</t>
+          <t>RAFAEL NARVAEZ CADENILLAS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-8.09733</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-79.0183</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-8.11777</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.04216</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>254737</t>
+          <t>252106</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>81523 JOSE IGNACIO CHOPITEA</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-8.0881</t>
+          <t>748</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-78.9691</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>-8.0954</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.01109</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>741238</t>
+          <t>252074</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>LOUIS PASTEUR</t>
+          <t>SAN LUIS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-8.09229</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-78.9574</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>-8.09733</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.0183</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>532918</t>
+          <t>252045</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>PERUANO AMERICANO ABRAHAM LINCOLN</t>
+          <t>SAN CARLOS Y SAN MARCELO</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-8.1068</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-79.03232</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>-8.10816</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.02894</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>639194</t>
+          <t>252012</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SANTA TERESITA</t>
+          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-8.08729</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-79.01659</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>-8.103440000000003</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.03421</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>250428</t>
+          <t>251994</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>UNIVERSAL SCHOOL</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-8.11348</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-79.02592</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-8.122</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-79.02307</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>749970</t>
+          <t>251951</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TRILCE DE SANTA MARIA</t>
+          <t>HERMANOS BLANCO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-8.12073</t>
+          <t>833</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-79.01998</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>-8.09752</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.03629</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,37 +5151,37 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>815385</t>
+          <t>251913</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FUTURA SCHOOLS - SEDE SAN ISIDRO</t>
+          <t>SANTA CLARA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-8.09522</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-79.05383</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>-8.10797</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.02731</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>831899</t>
+          <t>251847</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
+          <t>SAN GERARDO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-8.10006</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-79.03645</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>-8.10093</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-79.03815</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>250471</t>
+          <t>251828</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ADVENTISTA JOSE DE SAN MARTIN</t>
+          <t>WILLIAM HARVEY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-8.106696</t>
+          <t>419</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-79.025382</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>-8.12216</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.04248</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>250635</t>
+          <t>251772</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS SCHOOL</t>
+          <t>TALENTOS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-8.09298</t>
+          <t>812</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-79.01129</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>-8.13195</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.02874</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>251116</t>
+          <t>251753</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>SIR ALEXANDER FLEMING</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-8.11811</t>
+          <t>641</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-79.04256</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-8.12655</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.03494</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>657300</t>
+          <t>251606</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>INMACULADA VIRGEN DE LA PUERTA</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-8.102393</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-79.005064</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>-8.11012</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.01557</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>657338</t>
+          <t>251437</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INTEGRAL CLASS</t>
+          <t>PORTAL DE BELEN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-8.11736</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-79.03386</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>-8.09522</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.01618</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>658823</t>
+          <t>251362</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SAN JOSE SCHOOL</t>
+          <t>MARIA MADRE</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-8.09474</t>
+          <t>752</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-79.00501</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-8.08887</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.02103</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>658903</t>
+          <t>251277</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>TRILCE</t>
+          <t>MIS ABEJITAS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-8.10176</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-79.03523</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>-8.09656</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.04158</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>836566</t>
+          <t>251116</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SAN PEDRO</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-8.09687</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-79.02194</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>-8.11811</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-79.04256</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>249958</t>
+          <t>251102</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>80626 NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>MARCELINO CHAMPAGNAT</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-8.09003</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-79.01133</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-8.10272</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.03378</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>254921</t>
+          <t>250999</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>80048 JOSE EULOGIO GARRIDO</t>
+          <t>LAS CAPULLANAS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-8.147622</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-79.004128</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>-8.109920000000002</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.04155</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>668638</t>
+          <t>250819</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>MONTEVERDE</t>
+          <t>INGENIERIA</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-8.09207</t>
+          <t>656</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-79.04213</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>-8.121560000000002</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.03678</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>811448</t>
+          <t>250758</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO</t>
+          <t>EIFFEL SCHOOLS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-8.134278</t>
+          <t>601</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-79.025868</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>-8.109870000000003</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.00984</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>831903</t>
+          <t>250635</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS LORD KELVIN</t>
+          <t>CORAZON DE JESUS SCHOOL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-8.09717</t>
+          <t>244</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-79.03602</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>-8.092980000000003</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.01129</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,37 +6081,37 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>855183</t>
+          <t>250598</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO SAN ISIDRO</t>
+          <t>KINDERLAND</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-8.09571</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-79.04545</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>-8.12466</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.02916</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>250598</t>
+          <t>250490</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KINDERLAND</t>
+          <t>ALEJANDRO DEUSTUA</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-8.12466</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-79.02916</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-8.11717</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-79.02265</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>250070</t>
+          <t>250471</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>81008 / 81008 MUNICIPAL</t>
+          <t>ADVENTISTA JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-8.10647</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-79.022</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-8.106696</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.025382</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>250150</t>
+          <t>250428</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>81755 MEDALLA MILAGROSA</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-8.09283</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-79.0046</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>-8.11348</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.02592</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>294446</t>
+          <t>250414</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>80006 NUEVO PERU</t>
+          <t>SANTA MAGDALENA SOFIA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-8.10603</t>
+          <t>303</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-79.01125</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>-8.10909</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-79.03924</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,37 +6391,37 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>864192</t>
+          <t>250409</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>JHON D'ALEMBERT</t>
+          <t>LA ASUNCION</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-8.11058</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-79.03994</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>-8.10451</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-79.03596</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>540353</t>
+          <t>250391</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HANS HEINRICH BRUNING</t>
+          <t>SANTA MARIA DE GUADALUPE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-8.12683</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-79.02998</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>-8.121840000000002</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-79.01985</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>250758</t>
+          <t>250386</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>EIFFEL SCHOOLS</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-8.10987</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-79.00984</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>-8.118650000000002</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.03451</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6577,37 +6577,37 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>251362</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>MARIA MADRE</t>
+          <t>DANTE ALIGHIERI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-8.08887</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-79.02103</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-8.12272</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.02269</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>251828</t>
+          <t>250367</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>WILLIAM HARVEY</t>
+          <t>81584 EVERARDO ZAPATA SANTILLANA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-8.12216</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-79.04248</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>-8.09984</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.04849</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>252234</t>
+          <t>250353</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>MAYOR DE SAN MARCOS</t>
+          <t>MARIA NEGRON UGARTE</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-8.11657</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-79.02464</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>-8.10709</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.00709</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>824479</t>
+          <t>250348</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ALEXANDER GRAHAM BELL</t>
+          <t>82050 HUERTA BELLA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-8.10614</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-79.024557</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>-8.08828</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.0011</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,32 +6825,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>249977</t>
+          <t>250334</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>80882 JORGE CHAVEZ</t>
+          <t>MARIANO SANTOS MATEO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-8.09287</t>
+          <t>761</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-78.99507</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>-8.09545</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.04459</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>249915</t>
+          <t>250310</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>80017 ALFREDO TELLO SALAVARRIA</t>
+          <t>210 DULCE VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-8.1054</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-79.04109</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-8.11656</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.02179</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>250249</t>
+          <t>250268</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VICTOR ANDRES BELAUNDE</t>
+          <t>CECAT MARCIAL ACHARAN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-8.106057</t>
+          <t>623</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-79.023275</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>-8.12433</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.02456</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>250334</t>
+          <t>250249</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>MARIANO SANTOS MATEO</t>
+          <t>VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-8.09545</t>
+          <t>553</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-79.04459</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>-8.106057</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.023275</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>252106</t>
+          <t>250230</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-8.0954</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-79.01109</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>-8.11295</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-79.02612</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>250268</t>
+          <t>250225</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CECAT MARCIAL ACHARAN</t>
+          <t>SAN NICOLAS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-8.12433</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-79.02456</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>-8.109310000000002</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.03556</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>250819</t>
+          <t>250206</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>INGENIERIA</t>
+          <t>MARCIAL ACHARAN Y SMITH</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-8.12156</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-79.03678</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>-8.10785</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.02515</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>857714</t>
+          <t>250150</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AI APAEC</t>
+          <t>81755 MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-8.10891</t>
+          <t>558</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-79.00324</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>-8.09283</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.0046</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>252045</t>
+          <t>250145</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SAN CARLOS Y SAN MARCELO</t>
+          <t>81746 ALMIRANTE MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-8.10816</t>
+          <t>290</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-79.02894</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-8.111660000000002</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-79.04173</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,37 +7383,37 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>716875</t>
+          <t>250131</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EL CULTURAL AMERICAN SCHOOL</t>
+          <t>81653 NUESTRA SEÑORA DE MONTSERRAT</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-8.11726</t>
+          <t>339</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-79.03255</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>-8.12324</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-79.03235</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7455,22 +7455,22 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
           <t>-8.12436</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>-79.0284</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>255039</t>
+          <t>250094</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JOSE EMILIO LEFEBVRE FRANCOEUR</t>
+          <t>81011 ANTONIO RAYMONDI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-8.1725</t>
+          <t>962</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-79.00904</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>-8.10738</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.02935</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>250094</t>
+          <t>250089</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>81011 ANTONIO RAYMONDI</t>
+          <t>81010 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-8.10738</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-79.02935</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>-8.11834</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-79.04434</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>253436</t>
+          <t>250070</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>80033 JOSE OLAYA BALANDRA</t>
+          <t>81008 / 81008 MUNICIPAL</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-8.081</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-79.11715</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>-8.10647</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-79.022</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>861301</t>
+          <t>250065</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JUAN PABLO II</t>
+          <t>81007 MODELO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-8.09812</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-79.04136</t>
+          <t>104</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>-8.104905</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-79.0243</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>249982</t>
+          <t>250051</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>80892 LOS PINOS</t>
+          <t>81006 AMAUTA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-8.12433</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-79.04182</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>-8.1031</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-79.013</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>251951</t>
+          <t>250046</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>HERMANOS BLANCO</t>
+          <t>81005 JOSE CARLOS MARIATEGUI LA CHIRA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-8.09752</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-79.03629</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>-8.104134</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-79.014445</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>250372</t>
+          <t>250032</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>DANTE ALIGHIERI</t>
+          <t>81004 LA UNION</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-8.12272</t>
+          <t>353</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-79.02269</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>-8.107021</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-79.020124</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>250027</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>80002 ANTONIO TORRES ARAUJO</t>
+          <t>81003 CESAR ABRAHAM VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-8.1211</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-79.02563</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>-8.10813883264305</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-79.015925025085</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>251772</t>
+          <t>250013</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TALENTOS</t>
+          <t>81002 JAVIER HERAUD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-8.13195</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-79.02874</t>
+          <t>70</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>-8.1181</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-79.0195</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8065,32 +8065,32 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>249883</t>
+          <t>250008</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>80010 RICARDO PALMA</t>
+          <t>81001 REPUBLICA DE PANAMA</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>-8.10104</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>-79.02131</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>-8.117100000000002</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-79.0269</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8127,32 +8127,32 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>250027</t>
+          <t>249982</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>81003 CESAR ABRAHAM VALLEJO MENDOZA</t>
+          <t>80892 LOS PINOS</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>-8.10813883264305</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>-79.015925025085</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>-8.12433</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-79.04182</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>250008</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>81001 REPUBLICA DE PANAMA</t>
+          <t>80882 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-8.1171</t>
+          <t>668</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>-79.0269</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>-8.09287</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-78.99507</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -8251,32 +8251,32 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>831795</t>
+          <t>249963</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - TRUJILLO SANTA</t>
+          <t>80865 DANIEL HOYLE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>-8.0951</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>-79.01537</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>-8.09549</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-79.015024</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8313,32 +8313,32 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>249963</t>
+          <t>249958</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>80865 DANIEL HOYLE</t>
+          <t>80626 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>-8.09549</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>-79.015024</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>-8.09003</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-79.01133</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8375,32 +8375,32 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>251437</t>
+          <t>249944</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PORTAL DE BELEN</t>
+          <t>80077 ALCIDES CARREÑO BLAS</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>-8.09522</t>
+          <t>333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>-79.01618</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>-8.11234</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-79.02209</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -8437,32 +8437,32 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>252012</t>
+          <t>249939</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL PERPETUO SOCORRO</t>
+          <t>80019 CIRO ALEGRIA BAZAN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>-8.10344</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>-79.03421</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>-8.11425</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-79.00526</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>251994</t>
+          <t>249920</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UNIVERSAL SCHOOL</t>
+          <t>80018 REPUBLICA DE MEXICO</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>-8.122</t>
+          <t>560</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>-79.02307</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-8.104</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-79.0413</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8561,37 +8561,37 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>844279</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ECOLOGICA CESAR VALLEJO</t>
+          <t>80017 ALFREDO TELLO SALAVARRIA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>-8.08595</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>-79.01556</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>-8.1054</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-79.04109</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>250013</t>
+          <t>249897</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>81002 JAVIER HERAUD</t>
+          <t>80014 JUAN PABLO II</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>-8.1181</t>
+          <t>496</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>-79.0195</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>-8.108176</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-79.04526</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8685,42 +8685,42 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>250409</t>
+          <t>249883</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LA ASUNCION</t>
+          <t>80010 RICARDO PALMA</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>-8.10451</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>-79.03596</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>-8.10104</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>-79.02131</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8747,32 +8747,32 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>250386</t>
+          <t>249878</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>80008 REPUBLICA DE ARGENTINA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>-8.11865</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>-79.03451</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>-8.10496</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-79.00824</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8809,32 +8809,32 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>249878</t>
+          <t>249859</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>80008 REPUBLICA DE ARGENTINA</t>
+          <t>80005 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-8.10496</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>-79.00824</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>-8.114240000000002</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-79.01542</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -8871,32 +8871,32 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>251753</t>
+          <t>249840</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SIR ALEXANDER FLEMING</t>
+          <t>80003 ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-8.12655</t>
+          <t>337</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>-79.03494</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>-8.11725</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-79.02449</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -8933,37 +8933,37 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>252210</t>
+          <t>249835</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>80002 ANTONIO TORRES ARAUJO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-8.12409</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-79.02226</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-8.1211</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.02563</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8995,37 +8995,37 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>658205</t>
+          <t>249821</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>DESPERTAR</t>
+          <t>LICEO TRUJILLO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>-8.09941</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>-79.03782</t>
+          <t>117</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-8.09756</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.03293</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9057,32 +9057,32 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>255732</t>
+          <t>249816</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CLARETIANO</t>
+          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-8.12918</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>-79.03632</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>-8.122920000000002</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-79.02488</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>250353</t>
+          <t>249802</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>MARIA NEGRON UGARTE</t>
+          <t>GUSTAVO RIES</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-8.10709</t>
+          <t>1890</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-79.00709</t>
+          <t>87</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>-8.10189</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>-79.00614</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>249802</t>
+          <t>249755</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>GUSTAVO RIES</t>
+          <t>1733 MI MUNDO MARAVILLOSO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>-8.10189</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>-79.00614</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>-8.124510000000003</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>-79.03323</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -9243,32 +9243,32 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>251102</t>
+          <t>249581</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MARCELINO CHAMPAGNAT</t>
+          <t>1564 RADIANTES CAPULLITOS</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>-8.10272</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>-79.03378</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>-8.09104</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>-79.0093</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>254902</t>
+          <t>249576</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1721 LINA SKRABONJA</t>
+          <t>253 ISABEL HONORIO DE LAZARTE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-8.16952</t>
+          <t>371</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-79.01059</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-8.103120000000002</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.00797</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -9367,32 +9367,32 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>252125</t>
+          <t>249562</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>RAFAEL NARVAEZ CADENILLAS</t>
+          <t>252 NIÑO JESUS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-8.11777</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-79.04216</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>-8.10784</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-79.01593</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9429,32 +9429,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>744251</t>
+          <t>249557</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>81014 PEDRO MERCEDES UREÑA</t>
+          <t>215</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-8.11221643601271</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-79.0487275389903</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>-8.09693</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-79.02016</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -9491,37 +9491,37 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>252795</t>
+          <t>249543</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>80824 JOSE CARLOS MARIATEGUI</t>
+          <t>209 SANTA ANA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-8.08649</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-79.00268</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>-8.1168</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-79.0271</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9553,32 +9553,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>249816</t>
+          <t>249524</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JOSE FAUSTINO SANCHEZ CARRION</t>
+          <t>207 ALFREDO PINILLOS GOICOCHEA</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-8.12292</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-79.02488</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>-8.10787</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>-79.01937</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -9615,37 +9615,37 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>250230</t>
+          <t>249519</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SANTA ROSA</t>
+          <t>206 SABER Y FANTASIA CON MARIA</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-8.11295</t>
+          <t>201</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-79.02612</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>-8.10163</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-79.01118</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
